--- a/src/attributions/attributions_saliency_traj_201.xlsx
+++ b/src/attributions/attributions_saliency_traj_201.xlsx
@@ -1568,2278 +1568,2278 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3498007953166962</v>
+        <v>0.0003430286014918238</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1028686687350273</v>
+        <v>0.003393411636352539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7434614896774292</v>
+        <v>0.002164494246244431</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03683535382151604</v>
+        <v>0.003154582809656858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1554617583751678</v>
+        <v>0.001899321330711246</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1505424231290817</v>
+        <v>0.002958307508379221</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09042948484420776</v>
+        <v>0.000326598237734288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1798758059740067</v>
+        <v>0.002613465534523129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02705867774784565</v>
+        <v>0.001281850505620241</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1120177656412125</v>
+        <v>0.001084339455701411</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06708230078220367</v>
+        <v>0.005451483186334372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7186658382415771</v>
+        <v>0.002829434582963586</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04276508837938309</v>
+        <v>0.002759469207376242</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2838276624679565</v>
+        <v>0.00240883301012218</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01208141818642616</v>
+        <v>0.001374609651975334</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03506843745708466</v>
+        <v>0.001855236478149891</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06936972588300705</v>
+        <v>0.002557582687586546</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2307672798633575</v>
+        <v>7.163948612287641e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02590439468622208</v>
+        <v>0.0002018252853304148</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2214562445878983</v>
+        <v>0.0010919802589342</v>
       </c>
       <c r="U3" t="n">
-        <v>0.108134388923645</v>
+        <v>0.0005923740682192147</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1634978502988815</v>
+        <v>0.0002042226842604578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2128375172615051</v>
+        <v>0.0002449813473504037</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04673013463616371</v>
+        <v>0.000839809188619256</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06281040608882904</v>
+        <v>0.000232376711210236</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.07047098129987717</v>
+        <v>0.000742337026167661</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02706415019929409</v>
+        <v>0.001591495471075177</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01570993289351463</v>
+        <v>0.0004888461553491652</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1848142594099045</v>
+        <v>0.002008561510592699</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02347327768802643</v>
+        <v>0.001596670364961028</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.04616321623325348</v>
+        <v>0.0004047853872179985</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2242753058671951</v>
+        <v>0.0002582252491265535</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.05075225606560707</v>
+        <v>5.641952157020569e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.1003862470388412</v>
+        <v>0.0008272263221442699</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.06315038353204727</v>
+        <v>0.002756355796009302</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1600183546543121</v>
+        <v>0.001819222467020154</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0795852467417717</v>
+        <v>0.00101189105771482</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1462284177541733</v>
+        <v>0.002386429812759161</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1031381413340569</v>
+        <v>0.0007298471173271537</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.05972253903746605</v>
+        <v>0.001126577844843268</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1599386930465698</v>
+        <v>0.00259510800242424</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.02762690186500549</v>
+        <v>0.001247424632310867</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.608532905578613e-05</v>
+        <v>0.0006982177146710455</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.07502489537000656</v>
+        <v>8.958938997238874e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.05474948137998581</v>
+        <v>0.0005205164779908955</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1630977541208267</v>
+        <v>0.00135768624022603</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.02763079106807709</v>
+        <v>0.00484440615400672</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1994955390691757</v>
+        <v>0.0007223649881780148</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2811364531517029</v>
+        <v>0.0013158586807549</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.05844042077660561</v>
+        <v>0.001344846677966416</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.06882844865322113</v>
+        <v>0.0009629334090277553</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01239330321550369</v>
+        <v>0.0006421151338145137</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1331853717565536</v>
+        <v>0.002243957947939634</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1497567594051361</v>
+        <v>0.000126412880490534</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.04356423020362854</v>
+        <v>0.0004638920654542744</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.2173256278038025</v>
+        <v>0.001487438334152102</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.2510920166969299</v>
+        <v>0.0009182508219964802</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.5132294893264771</v>
+        <v>0.0004023712826892734</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.3454229235649109</v>
+        <v>0.003506150562316179</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.2019886076450348</v>
+        <v>0.0007979715010151267</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.007024038583040237</v>
+        <v>0.0002929327602032572</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1580396592617035</v>
+        <v>0.00156653649173677</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3225882947444916</v>
+        <v>0.0004171509062871337</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1379708796739578</v>
+        <v>3.266746352892369e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03605211526155472</v>
+        <v>0.0001496277691330761</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.02978180348873138</v>
+        <v>0.0002383949758950621</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.07967576384544373</v>
+        <v>0.0008651951793581247</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.07582670450210571</v>
+        <v>0.001090488862246275</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.04388786852359772</v>
+        <v>0.0003454966645222157</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.003053605556488037</v>
+        <v>0.0001526481355540454</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.06022526323795319</v>
+        <v>0.001238297205418348</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.002822689712047577</v>
+        <v>0.0009407794568687677</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.05464981868863106</v>
+        <v>0.0002271699195262045</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.08758608251810074</v>
+        <v>0.002541104797273874</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1961923241615295</v>
+        <v>0.0001740293519105762</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1849286258220673</v>
+        <v>0.0004710259672719985</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.01641310565173626</v>
+        <v>0.001893234089948237</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.08024932444095612</v>
+        <v>0.0001210577902384102</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.01570476219058037</v>
+        <v>0.0003313064808025956</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0271319504827261</v>
+        <v>0.0006116568110883236</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1321704238653183</v>
+        <v>0.002188842743635178</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0378120131790638</v>
+        <v>0.0001685204042587429</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.01486594974994659</v>
+        <v>0.00125069438945502</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.150558814406395</v>
+        <v>0.000570329837501049</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.07393212616443634</v>
+        <v>5.9456069720909e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.05934525653719902</v>
+        <v>0.0002697232412174344</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.02197922952473164</v>
+        <v>0.0009611655259504914</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.007029680535197258</v>
+        <v>0.00025422457838431</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.04696907848119736</v>
+        <v>0.0004722430021502078</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.02328960224986076</v>
+        <v>0.0003467799397185445</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1230172738432884</v>
+        <v>0.0005422916729003191</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1332275569438934</v>
+        <v>0.002568938303738832</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.02954603172838688</v>
+        <v>0.000814427447039634</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1522057354450226</v>
+        <v>0.00298184622079134</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.08613225072622299</v>
+        <v>2.764689270406961e-06</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1758129894733429</v>
+        <v>0.0003461267915554345</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1123808100819588</v>
+        <v>0.0005479426472447813</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.03663142397999763</v>
+        <v>0.002053960459306836</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.105953186750412</v>
+        <v>0.0005299199256114662</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02059539034962654</v>
+        <v>6.360058614518493e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.004272762686014175</v>
+        <v>0.000915515935048461</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.1401223391294479</v>
+        <v>0.0004757343558594584</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.07817491888999939</v>
+        <v>0.0001504020037828013</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.00837448425590992</v>
+        <v>4.493072628974915e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.03204385191202164</v>
+        <v>0.001232687849551439</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.01548733934760094</v>
+        <v>9.900378063321114e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0140281543135643</v>
+        <v>0.0006817415123805404</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04973492026329041</v>
+        <v>0.0006247959681786597</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1142385080456734</v>
+        <v>0.0006602658540941775</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1472117155790329</v>
+        <v>0.0009005219326354563</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.454008162021637</v>
+        <v>0.0008410750888288021</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.06626239418983459</v>
+        <v>0.001427791779860854</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.3137365281581879</v>
+        <v>0.003531596856191754</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.03938581049442291</v>
+        <v>0.002965205116197467</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.1968546211719513</v>
+        <v>0.0002591991797089577</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.00559541117399931</v>
+        <v>0.002221720991656184</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.02965499833226204</v>
+        <v>0.002015378559008241</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0542517714202404</v>
+        <v>0.001696988008916378</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1170996725559235</v>
+        <v>0.0003596550668589771</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.05218836665153503</v>
+        <v>0.0007133589824661613</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.075766421854496</v>
+        <v>0.0001408162934239954</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.127438873052597</v>
+        <v>0.001991331810131669</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05573781579732895</v>
+        <v>0.0003649418649729341</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.04882006347179413</v>
+        <v>0.0008275748696178198</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1068124324083328</v>
+        <v>0.001821459154598415</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.1927907317876816</v>
+        <v>0.0007729782955721021</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.008008353412151337</v>
+        <v>0.001547130756080151</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0804559588432312</v>
+        <v>0.001263055484741926</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.08059908449649811</v>
+        <v>0.0006503287586383522</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.04051681607961655</v>
+        <v>0.0002106089668814093</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.05755621939897537</v>
+        <v>0.002449356950819492</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1409544795751572</v>
+        <v>0.002801980590447783</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01789292693138123</v>
+        <v>2.270075856358744e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.06510477513074875</v>
+        <v>0.002626736415550113</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0373854823410511</v>
+        <v>0.0002773663145489991</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.06870707124471664</v>
+        <v>0.0008937239181250334</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1472367942333221</v>
+        <v>8.258502930402756e-07</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2149127125740051</v>
+        <v>3.657651541288942e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.1828034520149231</v>
+        <v>0.000676734431181103</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.05712626129388809</v>
+        <v>0.0009562407503835857</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1411892771720886</v>
+        <v>0.0004775820416398346</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.006384499371051788</v>
+        <v>0.0004187873273622245</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.01367869880050421</v>
+        <v>0.0006529153324663639</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02322180010378361</v>
+        <v>0.0004266934702172875</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.005019390489906073</v>
+        <v>0.000450699677458033</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1121107935905457</v>
+        <v>0.0008230716921389103</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.07688643038272858</v>
+        <v>0.000195981323486194</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01522259414196014</v>
+        <v>0.0002233715204056352</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1311749815940857</v>
+        <v>0.000469776161480695</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.09493465721607208</v>
+        <v>0.0004396717413328588</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.03647865355014801</v>
+        <v>9.786261944100261e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.02425725013017654</v>
+        <v>0.0005716723389923573</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.1445154845714569</v>
+        <v>0.001815845957025886</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.03052367642521858</v>
+        <v>0.000166937432368286</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0547047033905983</v>
+        <v>0.001429860014468431</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.1535998433828354</v>
+        <v>0.0006226352415978909</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0642269104719162</v>
+        <v>0.0001731780357658863</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01387753803282976</v>
+        <v>3.487640060484409e-05</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03383021429181099</v>
+        <v>0.0009980936301872134</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.005129233002662659</v>
+        <v>0.000275050348136574</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.007503356784582138</v>
+        <v>0.0007922157528810203</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.01997093856334686</v>
+        <v>0.0008116148528642952</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.1061587259173393</v>
+        <v>0.0008660042658448219</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.09712623059749603</v>
+        <v>0.0007169437012635171</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.02726328186690807</v>
+        <v>0.001462826272472739</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.07005930691957474</v>
+        <v>0.0006011697114445269</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.01056524738669395</v>
+        <v>0.001328228041529655</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.001852004788815975</v>
+        <v>8.87463174876757e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.04142885282635689</v>
+        <v>0.000645136518869549</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.06881142407655716</v>
+        <v>0.0004068156413268298</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.03998234868049622</v>
+        <v>0.001337649300694466</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0540725365281105</v>
+        <v>0.0004752393579110503</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.02474343776702881</v>
+        <v>0.0002169662620872259</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.04714220017194748</v>
+        <v>0.0004803641641046852</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1810938119888306</v>
+        <v>0.001081259339116514</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.09692122787237167</v>
+        <v>0.003446235321462154</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.02161380834877491</v>
+        <v>0.00311706168577075</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03972036391496658</v>
+        <v>0.0009552791016176343</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2411503493785858</v>
+        <v>0.0003498212900012732</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.02315345034003258</v>
+        <v>0.001440198859199882</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.07562290877103806</v>
+        <v>0.0001802367332857102</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.06371217966079712</v>
+        <v>0.001012664055451751</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.183578833937645</v>
+        <v>0.0009920472512021661</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.04931045323610306</v>
+        <v>0.001920770853757858</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.06891076266765594</v>
+        <v>0.001067523029632866</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.08334968239068985</v>
+        <v>0.0003667044802568853</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.05254943668842316</v>
+        <v>0.0003814027295447886</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.05884883180260658</v>
+        <v>0.001494022784754634</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.04742716252803802</v>
+        <v>0.0006191122229211032</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.009609529748558998</v>
+        <v>0.2871946692466736</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2950366139411926</v>
+        <v>0.6120863556861877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05386928468942642</v>
+        <v>0.1219547986984253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.105328343808651</v>
+        <v>0.1885143220424652</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3594523072242737</v>
+        <v>0.2011814117431641</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06248387321829796</v>
+        <v>0.4439312517642975</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1345805823802948</v>
+        <v>0.09018170833587646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.101901687681675</v>
+        <v>0.3641989827156067</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01383042801171541</v>
+        <v>0.07159184664487839</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06158069893717766</v>
+        <v>0.330099880695343</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1953791826963425</v>
+        <v>0.5657132863998413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02685128524899483</v>
+        <v>0.2129665166139603</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005910497158765793</v>
+        <v>0.3151567280292511</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3020245432853699</v>
+        <v>0.385590136051178</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05818870291113853</v>
+        <v>0.325152724981308</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1507167965173721</v>
+        <v>0.2212397307157516</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02400314062833786</v>
+        <v>0.3243687748908997</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002803303301334381</v>
+        <v>0.2385495007038116</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01703566499054432</v>
+        <v>0.00624706270173192</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04940268397331238</v>
+        <v>0.0218046773225069</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03363604843616486</v>
+        <v>0.06354688107967377</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05810718610882759</v>
+        <v>0.04893051087856293</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1175371631979942</v>
+        <v>0.009369632229208946</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06642633676528931</v>
+        <v>0.05414177477359772</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04808911681175232</v>
+        <v>0.01110642030835152</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.031728845089674</v>
+        <v>0.1605780422687531</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0009145066142082214</v>
+        <v>0.06630414724349976</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03844882920384407</v>
+        <v>0.05244060233235359</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02148154750466347</v>
+        <v>0.2386466264724731</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0008400722872465849</v>
+        <v>0.03847262635827065</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.03364962711930275</v>
+        <v>0.03449932858347893</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02887188643217087</v>
+        <v>0.008495461195707321</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02734301798045635</v>
+        <v>0.03886597603559494</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.03913028165698051</v>
+        <v>0.001852203160524368</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0109760407358408</v>
+        <v>0.0164804570376873</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02220779284834862</v>
+        <v>0.03389331698417664</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02517749927937984</v>
+        <v>0.06534326076507568</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08959612250328064</v>
+        <v>0.2146337330341339</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.02035963535308838</v>
+        <v>0.1945007741451263</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.01926542446017265</v>
+        <v>0.1093734875321388</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.01653128117322922</v>
+        <v>0.1492791026830673</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05541880801320076</v>
+        <v>0.02837774530053139</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.02486972697079182</v>
+        <v>0.04248050600290298</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.03520042821764946</v>
+        <v>0.124113142490387</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001636081375181675</v>
+        <v>0.01967953518033028</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01642127893865108</v>
+        <v>0.1592035591602325</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2172432541847229</v>
+        <v>0.2913427650928497</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.05689528957009315</v>
+        <v>0.1093957722187042</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.06868424266576767</v>
+        <v>0.16654372215271</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1991010159254074</v>
+        <v>0.3275448083877563</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.05430764704942703</v>
+        <v>0.1623777896165848</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002329161390662193</v>
+        <v>0.06276936084032059</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.02630947344005108</v>
+        <v>0.005979673936963081</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02168788015842438</v>
+        <v>0.01786432042717934</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.02257546037435532</v>
+        <v>0.01298746652901173</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0418967604637146</v>
+        <v>0.1069684028625488</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.01809315569698811</v>
+        <v>0.1409065425395966</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002233251929283142</v>
+        <v>0.02582674100995064</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1456615924835205</v>
+        <v>0.03904954716563225</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01899691671133041</v>
+        <v>0.2115176469087601</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.04808111488819122</v>
+        <v>0.0297398567199707</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001879740506410599</v>
+        <v>0.0517345629632473</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001564042642712593</v>
+        <v>0.07963073253631592</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.06884466111660004</v>
+        <v>0.06415830552577972</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02084465511143208</v>
+        <v>0.02129865810275078</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01078776828944683</v>
+        <v>0.04011259227991104</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.03556054830551147</v>
+        <v>0.03251630812883377</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02842999994754791</v>
+        <v>0.0438300296664238</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.03876221552491188</v>
+        <v>0.02893802523612976</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.02614660002291203</v>
+        <v>0.06150652095675468</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.025959312915802</v>
+        <v>0.06938128918409348</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.004713238216936588</v>
+        <v>0.03341104835271835</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.04193562641739845</v>
+        <v>0.1050878316164017</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1695095151662827</v>
+        <v>0.2105913460254669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02863865904510021</v>
+        <v>0.08460314571857452</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.05152993649244308</v>
+        <v>0.1182461008429527</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1614287942647934</v>
+        <v>0.08177055418491364</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1081554442644119</v>
+        <v>0.1158617436885834</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.03308822214603424</v>
+        <v>0.07500202208757401</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01637035608291626</v>
+        <v>0.1086097583174706</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.009806424379348755</v>
+        <v>0.04254006966948509</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.02015622146427631</v>
+        <v>0.06817266345024109</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.03026322089135647</v>
+        <v>0.219511941075325</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.01871997863054276</v>
+        <v>0.01494111213833094</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02011477947235107</v>
+        <v>0.07713621854782104</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.05589455738663673</v>
+        <v>0.01367587596178055</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04264265298843384</v>
+        <v>0.1370000392198563</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.000896054320037365</v>
+        <v>0.03209094703197479</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.01409429311752319</v>
+        <v>0.08476980775594711</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.01123412139713764</v>
+        <v>0.02953973785042763</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.01857389509677887</v>
+        <v>0.08615319430828094</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02442282438278198</v>
+        <v>0.3034031987190247</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.009679177775979042</v>
+        <v>0.1253158748149872</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.05011821910738945</v>
+        <v>0.1845837831497192</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.06061656773090363</v>
+        <v>0.01169278100132942</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.007250799797475338</v>
+        <v>0.09150079637765884</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.08485640585422516</v>
+        <v>0.0008081961423158646</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.07629764825105667</v>
+        <v>0.02145626023411751</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.01291217468678951</v>
+        <v>0.08966062963008881</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.02104876935482025</v>
+        <v>0.07460489124059677</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.01792414486408234</v>
+        <v>0.2071662247180939</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.01614526472985744</v>
+        <v>0.005321856588125229</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02674506790935993</v>
+        <v>0.08574202656745911</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.05315770581364632</v>
+        <v>0.01766827516257763</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.06481778621673584</v>
+        <v>0.1292517632246017</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01174418721348047</v>
+        <v>0.04296255484223366</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.009105485863983631</v>
+        <v>0.1103910505771637</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.005056065041571856</v>
+        <v>0.01631144993007183</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.01998263224959373</v>
+        <v>0.006049314513802528</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.102499932050705</v>
+        <v>0.1860162764787674</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.01652976870536804</v>
+        <v>0.06565326452255249</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0810864120721817</v>
+        <v>0.1194927096366882</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002775819972157478</v>
+        <v>0.09604771435260773</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02849125675857067</v>
+        <v>0.2254922240972519</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.08661255240440369</v>
+        <v>0.05763936787843704</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.04391998052597046</v>
+        <v>0.1483524888753891</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.01400216482579708</v>
+        <v>0.1659301519393921</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.06067905575037003</v>
+        <v>0.03430657088756561</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.04343065246939659</v>
+        <v>0.1255358457565308</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.05829508975148201</v>
+        <v>0.06130941212177277</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.07296121865510941</v>
+        <v>0.09403227269649506</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.03850466758012772</v>
+        <v>0.01041095890104771</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01317153871059418</v>
+        <v>0.1091204434633255</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001633758656680584</v>
+        <v>0.02124779671430588</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.07352384924888611</v>
+        <v>0.08751314878463745</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.01299867406487465</v>
+        <v>0.09780748933553696</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.004871226847171783</v>
+        <v>0.05624500289559364</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.04376699775457382</v>
+        <v>0.06552591919898987</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.02701165899634361</v>
+        <v>0.1444019377231598</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0116847101598978</v>
+        <v>0.1228067129850388</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.05884658545255661</v>
+        <v>0.2208948880434036</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01920310221612453</v>
+        <v>0.2480801492929459</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.007747902534902096</v>
+        <v>0.100792683660984</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.04068003967404366</v>
+        <v>0.1992898136377335</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.03178737312555313</v>
+        <v>0.1917766183614731</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.01935024932026863</v>
+        <v>0.01546710729598999</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.008892068639397621</v>
+        <v>0.1317513734102249</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.004937490448355675</v>
+        <v>0.1425661593675613</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.004840406123548746</v>
+        <v>0.01198477111756802</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.06279261410236359</v>
+        <v>0.01165981404483318</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.04157833009958267</v>
+        <v>0.1523875296115875</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.01122681889683008</v>
+        <v>0.00588667206466198</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.01081357151269913</v>
+        <v>0.05202237889170647</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.009363701567053795</v>
+        <v>0.07115384936332703</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.009883741848170757</v>
+        <v>0.08959913998842239</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.02878552675247192</v>
+        <v>0.1494419574737549</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.002242653165012598</v>
+        <v>0.1098272949457169</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.005539653822779655</v>
+        <v>0.03486167266964912</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.01209314819425344</v>
+        <v>0.08054160326719284</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.1921326369047165</v>
+        <v>0.04491722211241722</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.00576379569247365</v>
+        <v>0.01318323239684105</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.06994136422872543</v>
+        <v>0.1165631115436554</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.03061483986675739</v>
+        <v>0.1398923993110657</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.02354095503687859</v>
+        <v>0.07316703349351883</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.008565459400415421</v>
+        <v>0.2579018473625183</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.02346383221447468</v>
+        <v>0.006302673369646072</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.03059175983071327</v>
+        <v>0.09739506244659424</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.05664614588022232</v>
+        <v>0.006386091932654381</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.04981651529669762</v>
+        <v>0.09264352172613144</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.004729202017188072</v>
+        <v>0.01928068138659</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.01965029165148735</v>
+        <v>0.1355099231004715</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.002008849289268255</v>
+        <v>0.006515901535749435</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.02548776566982269</v>
+        <v>0.009954463690519333</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.06077080592513084</v>
+        <v>0.1562734842300415</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.01212548278272152</v>
+        <v>0.01446213945746422</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05585398897528648</v>
+        <v>0.08779995143413544</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.005233101546764374</v>
+        <v>0.1323779821395874</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.04402243345975876</v>
+        <v>0.05824220925569534</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0002884399145841599</v>
+        <v>0.1334807723760605</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.00165865570306778</v>
+        <v>0.1234461516141891</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.01832086779177189</v>
+        <v>0.06207869574427605</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.02043144404888153</v>
+        <v>0.1055932343006134</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.07050517946481705</v>
+        <v>0.3384717106819153</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.03753751516342163</v>
+        <v>0.3622070550918579</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.03850623965263367</v>
+        <v>0.1322129517793655</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.1418686211109161</v>
+        <v>0.06200690567493439</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0158933587372303</v>
+        <v>0.07286611944437027</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.02650370821356773</v>
+        <v>0.1827599108219147</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.03470540791749954</v>
+        <v>0.1318057924509048</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.02219202928245068</v>
+        <v>0.1277288794517517</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.03313335031270981</v>
+        <v>0.1403766870498657</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.013252935372293</v>
+        <v>0.01200409978628159</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.05949127301573753</v>
+        <v>0.03981913626194</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.03819471597671509</v>
+        <v>0.03468360751867294</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1063447147607803</v>
+        <v>0.02817298285663128</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.03647076338529587</v>
+        <v>0.03165001794695854</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.08791500329971313</v>
+        <v>0.02263637632131577</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.008098900318145752</v>
+        <v>0.1746212244033813</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.01010201964527369</v>
+        <v>0.1680641621351242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.851793245412409e-05</v>
+        <v>0.001146208611316979</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002023112261667848</v>
+        <v>0.04004538059234619</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000124317390145734</v>
+        <v>0.02042381465435028</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001058741938322783</v>
+        <v>0.01131251454353333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001237376360222697</v>
+        <v>0.003409671364352107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000787760189268738</v>
+        <v>0.02144585177302361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003025557089131325</v>
+        <v>0.0006834217347204685</v>
       </c>
       <c r="H5" t="n">
-        <v>2.441815013298765e-05</v>
+        <v>0.0003809317131526768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002158983843401074</v>
+        <v>0.01393758412450552</v>
       </c>
       <c r="J5" t="n">
-        <v>3.058527363464236e-05</v>
+        <v>0.002049499191343784</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001691185287199914</v>
+        <v>0.04259848594665527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001633921201573685</v>
+        <v>0.02496886253356934</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002328296832274646</v>
+        <v>0.01891091838479042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0008064024732448161</v>
+        <v>0.002640092745423317</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0004626454028766602</v>
+        <v>0.01311876345425844</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0005704559735022485</v>
+        <v>0.001695340499281883</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003637755871750414</v>
+        <v>0.007150540128350258</v>
       </c>
       <c r="R5" t="n">
-        <v>7.176625513238832e-05</v>
+        <v>0.008867355063557625</v>
       </c>
       <c r="S5" t="n">
-        <v>5.113893712405115e-05</v>
+        <v>0.003418980166316032</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0001054455060511827</v>
+        <v>0.00676227081567049</v>
       </c>
       <c r="U5" t="n">
-        <v>1.697782863629982e-05</v>
+        <v>0.01034898031502962</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003336518711876124</v>
+        <v>0.0004741201119031757</v>
       </c>
       <c r="W5" t="n">
-        <v>5.953882009634981e-07</v>
+        <v>0.001905860379338264</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0001595807116245851</v>
+        <v>0.01100296806544065</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002458253584336489</v>
+        <v>0.001759763574227691</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000106243351183366</v>
+        <v>0.0004480956413317472</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0002913595526479185</v>
+        <v>0.006101422011852264</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.396018968895078e-05</v>
+        <v>0.003771432675421238</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.081680941046216e-05</v>
+        <v>0.005925072357058525</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002383929386269301</v>
+        <v>0.0008899817476049066</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0004465369565878063</v>
+        <v>0.01402177941054106</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002372492017457262</v>
+        <v>0.0136293563991785</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0002042418200289831</v>
+        <v>0.002984666964039207</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.694441016297787e-05</v>
+        <v>0.004640840925276279</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003505935601424426</v>
+        <v>0.002574703888967633</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0002171149535570294</v>
+        <v>0.005424290895462036</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0001004216464934871</v>
+        <v>0.0008054006029851735</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0003426907060202211</v>
+        <v>0.007733161561191082</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001094039471354336</v>
+        <v>0.007198232691735029</v>
       </c>
       <c r="AN5" t="n">
-        <v>4.854981307289563e-05</v>
+        <v>0.00565354572609067</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.665994750510436e-05</v>
+        <v>0.01583751477301121</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.000244864058913663</v>
+        <v>0.007207273505628109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.389144255081192e-05</v>
+        <v>0.003496623132377863</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0001984361006179824</v>
+        <v>0.0007271289359778166</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001807198277674615</v>
+        <v>0.0009041515295393765</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0002818388747982681</v>
+        <v>0.001242289901711047</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.00105719524435699</v>
+        <v>0.02911025285720825</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.209384759538807e-06</v>
+        <v>0.003244397230446339</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0009880943689495325</v>
+        <v>0.012147206813097</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0008341582724824548</v>
+        <v>0.001480159116908908</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0004823039344046265</v>
+        <v>0.007843509316444397</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0003755313227884471</v>
+        <v>0.0005363819655030966</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001675768144195899</v>
+        <v>0.0007569470908492804</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0003868514904752374</v>
+        <v>0.004850124008953571</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0002073123323498294</v>
+        <v>0.004749380517750978</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0002962073776870966</v>
+        <v>0.004128864035010338</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0002674198476597667</v>
+        <v>0.01145871169865131</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.426637214142829e-05</v>
+        <v>0.005748019553720951</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0006820362177677453</v>
+        <v>0.003009159583598375</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0002710165863391012</v>
+        <v>0.01427867449820042</v>
       </c>
       <c r="BI5" t="n">
-        <v>6.198891060194001e-05</v>
+        <v>0.002728150226175785</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0004262124130036682</v>
+        <v>0.003353636479005218</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0001950269361259416</v>
+        <v>0.007482642307877541</v>
       </c>
       <c r="BL5" t="n">
-        <v>8.25935130706057e-05</v>
+        <v>0.002054629381746054</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001793535775505006</v>
+        <v>0.005034828558564186</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001585024583619088</v>
+        <v>0.004773910623043776</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.556044586934149e-05</v>
+        <v>0.007429879158735275</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0004958437057211995</v>
+        <v>0.002722110832110047</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0001348278892692178</v>
+        <v>0.0002526489552110434</v>
       </c>
       <c r="BR5" t="n">
-        <v>2.606377165648155e-05</v>
+        <v>0.003168279305100441</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.000321641331538558</v>
+        <v>0.002859186846762896</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.907117206836119e-05</v>
+        <v>0.002922711428254843</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0002604606270324439</v>
+        <v>0.001583275734446943</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0007387830410152674</v>
+        <v>0.01942707598209381</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.088938294444233e-05</v>
+        <v>0.001450897892937064</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0003662765375338495</v>
+        <v>0.006478158291429281</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0003828006447292864</v>
+        <v>0.002444566693156958</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8.905321010388434e-05</v>
+        <v>0.01328148785978556</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002087751345243305</v>
+        <v>0.0002783581148833036</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.773087104898877e-05</v>
+        <v>0.000291735865175724</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0002664797066245228</v>
+        <v>0.007636349648237228</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.22645132150501e-05</v>
+        <v>0.001030981540679932</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0002027602458838373</v>
+        <v>0.01317261345684528</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.659856732469052e-05</v>
+        <v>0.008529039099812508</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0002217259025201201</v>
+        <v>0.00518741924315691</v>
       </c>
       <c r="CH5" t="n">
-        <v>6.096911238273606e-05</v>
+        <v>2.848493750207126e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001331845851382241</v>
+        <v>0.0001416132436133921</v>
       </c>
       <c r="CJ5" t="n">
-        <v>4.460851414478384e-06</v>
+        <v>0.0007678305264562368</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.999754987191409e-05</v>
+        <v>0.001205675303936005</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0002129139029420912</v>
+        <v>0.003826464526355267</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.862874887592625e-05</v>
+        <v>0.004798974376171827</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0002915039949584752</v>
+        <v>0.01064490433782339</v>
       </c>
       <c r="CO5" t="n">
-        <v>8.43620509840548e-05</v>
+        <v>0.004473008681088686</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0004821795737370849</v>
+        <v>0.01165644451975822</v>
       </c>
       <c r="CQ5" t="n">
-        <v>8.215494744945318e-05</v>
+        <v>0.003843365702778101</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0004221690469421446</v>
+        <v>0.009884949773550034</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.000552272074855864</v>
+        <v>0.00289154564961791</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0002619011502247304</v>
+        <v>0.0001739915460348129</v>
       </c>
       <c r="CU5" t="n">
-        <v>9.573502757120878e-05</v>
+        <v>0.005150565877556801</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.937299202836584e-06</v>
+        <v>0.00112474721390754</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0002473648055456579</v>
+        <v>0.01375034172087908</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0001302573800785467</v>
+        <v>0.008980890735983849</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0003052015963476151</v>
+        <v>0.005149636417627335</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001092843231162988</v>
+        <v>0.001481753424741328</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002201816969318315</v>
+        <v>0.001743072993122041</v>
       </c>
       <c r="DB5" t="n">
-        <v>7.026336970739067e-05</v>
+        <v>0.0002594356192275882</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0001011342246783897</v>
+        <v>0.0004613917553797364</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001818935415940359</v>
+        <v>0.005044052377343178</v>
       </c>
       <c r="DE5" t="n">
-        <v>9.282289101975039e-05</v>
+        <v>0.005884065292775631</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0003774634678848088</v>
+        <v>0.01863201521337032</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0002200860617449507</v>
+        <v>0.01251542754471302</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.001354398322291672</v>
+        <v>0.01065594796091318</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0009718362125568092</v>
+        <v>0.005344109144061804</v>
       </c>
       <c r="DJ5" t="n">
-        <v>6.743392441421747e-05</v>
+        <v>0.002616670913994312</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0004874771402683109</v>
+        <v>0.001453385222703218</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.000699876865837723</v>
+        <v>0.009620760567486286</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001042717485688627</v>
+        <v>0.008087361231446266</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002380973019171506</v>
+        <v>0.001258525182493031</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0001891873398562893</v>
+        <v>0.004538852255791426</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0005023335688747466</v>
+        <v>0.00506623275578022</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.000119866817840375</v>
+        <v>0.002441250253468752</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0001027449470711872</v>
+        <v>0.004119386896491051</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0001538310170872137</v>
+        <v>0.007881062105298042</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001135014172177762</v>
+        <v>0.0008880752138793468</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001510572910774499</v>
+        <v>0.0001013127621263266</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0002577322593424469</v>
+        <v>0.007514766417443752</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001152884433395229</v>
+        <v>0.003729383694007993</v>
       </c>
       <c r="DX5" t="n">
-        <v>3.483884211163968e-05</v>
+        <v>0.007402560207992792</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0003949866513721645</v>
+        <v>0.006571678910404444</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002315038291271776</v>
+        <v>0.003847970860078931</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.697270636213943e-05</v>
+        <v>0.009647827595472336</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001586223079357296</v>
+        <v>0.007480303756892681</v>
       </c>
       <c r="EC5" t="n">
-        <v>7.775693666189909e-05</v>
+        <v>0.0003550848632585257</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0002323570370208472</v>
+        <v>0.005503323394805193</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0001479299244238064</v>
+        <v>0.005606187041848898</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0002036591904470697</v>
+        <v>0.001606122357770801</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0001427118550054729</v>
+        <v>0.01299998350441456</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002239669993286952</v>
+        <v>0.005586283281445503</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.733160727075301e-05</v>
+        <v>0.003472137730568647</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0003277658834122121</v>
+        <v>0.0003739791281986982</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0002619909646455199</v>
+        <v>0.005869455635547638</v>
       </c>
       <c r="EL5" t="n">
-        <v>3.373934305272996e-07</v>
+        <v>0.001232987502589822</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.08624626591336e-05</v>
+        <v>0.001000942895188928</v>
       </c>
       <c r="EN5" t="n">
-        <v>6.990891415625811e-05</v>
+        <v>0.004806666634976864</v>
       </c>
       <c r="EO5" t="n">
-        <v>3.415310857235454e-05</v>
+        <v>0.0001784066116670147</v>
       </c>
       <c r="EP5" t="n">
-        <v>8.72476175572956e-06</v>
+        <v>0.0005609032232314348</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001201421182486229</v>
+        <v>0.004065204877406359</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001520471560070291</v>
+        <v>0.001765619497746229</v>
       </c>
       <c r="ES5" t="n">
-        <v>7.760183507343754e-05</v>
+        <v>0.0004722622688859701</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0003563420032151043</v>
+        <v>0.0001692537916824222</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0001574520574649796</v>
+        <v>0.00308009865693748</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0002205854980275035</v>
+        <v>0.001799716148525476</v>
       </c>
       <c r="EW5" t="n">
-        <v>9.468345524510369e-05</v>
+        <v>0.005464470013976097</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.066695014946163e-05</v>
+        <v>0.001498944358900189</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0002259644534206018</v>
+        <v>0.01444796752184629</v>
       </c>
       <c r="EZ5" t="n">
-        <v>4.820678077521734e-05</v>
+        <v>0.007415310014039278</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0002542333968449384</v>
+        <v>0.006635788828134537</v>
       </c>
       <c r="FB5" t="n">
-        <v>3.820436177193187e-06</v>
+        <v>0.001571189612150192</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0001386741059832275</v>
+        <v>0.002575919963419437</v>
       </c>
       <c r="FD5" t="n">
-        <v>5.265138679533266e-05</v>
+        <v>0.0003133367281407118</v>
       </c>
       <c r="FE5" t="n">
-        <v>6.502724863821641e-05</v>
+        <v>0.001339352573268116</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0002320414932910353</v>
+        <v>0.004715568386018276</v>
       </c>
       <c r="FG5" t="n">
-        <v>6.998135359026492e-05</v>
+        <v>0.000419755291659385</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0003029096114914864</v>
+        <v>0.01154069881886244</v>
       </c>
       <c r="FI5" t="n">
-        <v>3.507511792122386e-05</v>
+        <v>0.0005264529027044773</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0003342957061249763</v>
+        <v>0.004297071602195501</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0002094650990329683</v>
+        <v>0.009063743986189365</v>
       </c>
       <c r="FL5" t="n">
-        <v>3.555732837412506e-05</v>
+        <v>0.003769171424210072</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.992333510424942e-06</v>
+        <v>0.002297345083206892</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0002659710880834609</v>
+        <v>0.001297210576012731</v>
       </c>
       <c r="FO5" t="n">
-        <v>7.803125481586903e-05</v>
+        <v>0.008665613830089569</v>
       </c>
       <c r="FP5" t="n">
-        <v>5.362738738767803e-05</v>
+        <v>0.00152491801418364</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0004159285745117813</v>
+        <v>0.01433574594557285</v>
       </c>
       <c r="FR5" t="n">
-        <v>4.759881994687021e-05</v>
+        <v>0.01094720233231783</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0005400276859290898</v>
+        <v>0.01378684677183628</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0004385832289699465</v>
+        <v>0.0001342273317277431</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001441230706404895</v>
+        <v>0.01056727208197117</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0001180316030513495</v>
+        <v>0.003592680906876922</v>
       </c>
       <c r="FW5" t="n">
-        <v>4.857670865021646e-05</v>
+        <v>0.0007324698381125927</v>
       </c>
       <c r="FX5" t="n">
-        <v>2.49797958531417e-05</v>
+        <v>0.0007427036762237549</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.000100615419796668</v>
+        <v>0.01061617024242878</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.539440745546017e-06</v>
+        <v>0.01510368939489126</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0001011327403830364</v>
+        <v>0.01997634023427963</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0004033126460853964</v>
+        <v>0.003404352813959122</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0004721357836388052</v>
+        <v>0.002945682965219021</v>
       </c>
       <c r="GD5" t="n">
-        <v>5.487503585754894e-05</v>
+        <v>0.007005093619227409</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0006084403139539063</v>
+        <v>0.005823361687362194</v>
       </c>
       <c r="GF5" t="n">
-        <v>9.944164048647508e-05</v>
+        <v>0.007515741512179375</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.680705827311613e-05</v>
+        <v>0.004053627140820026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.02308423258364201</v>
+        <v>0.0001379222376272082</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2700941860675812</v>
+        <v>0.00060332688735798</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0121845779940486</v>
+        <v>2.386633786954917e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1400018483400345</v>
+        <v>0.0002245729410788044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03652042523026466</v>
+        <v>5.665910430252552e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2636938095092773</v>
+        <v>0.0004183195997029543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004772966727614403</v>
+        <v>8.532208448741585e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09588789939880371</v>
+        <v>6.466812192229554e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03361897543072701</v>
+        <v>2.750852218014188e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05820509791374207</v>
+        <v>5.813430470880121e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2540064752101898</v>
+        <v>0.0007246483583003283</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00303701451048255</v>
+        <v>7.536767225246876e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1028423234820366</v>
+        <v>0.0003814349474851042</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001460518687963486</v>
+        <v>0.0001224307052325457</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2426442503929138</v>
+        <v>0.0004337758291512728</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01864532195031643</v>
+        <v>1.376226464344654e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04840560629963875</v>
+        <v>8.486683509545401e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009806429035961628</v>
+        <v>7.047014514682814e-05</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01251366175711155</v>
+        <v>3.325661236885935e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01337157469242811</v>
+        <v>9.048234642250463e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02460465952754021</v>
+        <v>1.873733708634973e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04296129196882248</v>
+        <v>4.147693834966049e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07205949723720551</v>
+        <v>3.375276355654933e-05</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01753161661326885</v>
+        <v>7.472515426343307e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02438260987401009</v>
+        <v>4.785719283972867e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.06725317239761353</v>
+        <v>0.000193166866665706</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04252458363771439</v>
+        <v>5.251072252576705e-06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.005329102277755737</v>
+        <v>7.954739703563973e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01731729507446289</v>
+        <v>5.514948134077713e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01848237402737141</v>
+        <v>2.650616079336032e-05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01523731276392937</v>
+        <v>0.0001455357414670289</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02967013418674469</v>
+        <v>7.519321661675349e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02477460727095604</v>
+        <v>0.0001449472911190242</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.01395186129957438</v>
+        <v>6.234004104044288e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.006000030785799026</v>
+        <v>0.0002691161644179374</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02479415200650692</v>
+        <v>4.488327977014706e-05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.02446242980659008</v>
+        <v>0.0001086957345250994</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04352667927742004</v>
+        <v>6.493673572549596e-05</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001667232252657413</v>
+        <v>5.82121720071882e-06</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.006943641230463982</v>
+        <v>6.377438694471493e-05</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.001152393873780966</v>
+        <v>1.137665458372794e-05</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03269098326563835</v>
+        <v>1.580831667524762e-05</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.002945689484477043</v>
+        <v>4.628689930541441e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0170839000493288</v>
+        <v>0.0001864376827143133</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.02470722794532776</v>
+        <v>2.672809387149755e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.02915184944868088</v>
+        <v>0.0001250760979019105</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1975713521242142</v>
+        <v>0.0004507347766775638</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.001950948499143124</v>
+        <v>8.599760622018948e-05</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.05770295858383179</v>
+        <v>0.0001190951152238995</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.02765282057225704</v>
+        <v>0.0002676100993994623</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1364703774452209</v>
+        <v>0.0002266863157274202</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01165301818400621</v>
+        <v>1.267196239496116e-05</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.02164324559271336</v>
+        <v>2.15978088817792e-05</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0653376579284668</v>
+        <v>6.117662996985018e-05</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.02452132478356361</v>
+        <v>7.299918797798455e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0472516342997551</v>
+        <v>8.508354949299246e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.06001319363713264</v>
+        <v>1.384667848469689e-05</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.009381678886711597</v>
+        <v>0.000150211009895429</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.05216707661747932</v>
+        <v>9.513106488157064e-05</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.08037464320659637</v>
+        <v>9.948742808774114e-05</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01857436820864677</v>
+        <v>3.327930244267918e-05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.01689907163381577</v>
+        <v>0.0001095314437407069</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.001865943893790245</v>
+        <v>6.083115295041353e-05</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.001097093801945448</v>
+        <v>3.787861351156607e-05</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.07127029448747635</v>
+        <v>8.217164577217773e-06</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01000308804214001</v>
+        <v>4.475213427213021e-05</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02312815375626087</v>
+        <v>9.329060412710533e-05</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.006425327155739069</v>
+        <v>6.112373375799507e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.00216773385182023</v>
+        <v>2.496818706276827e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.01239768415689468</v>
+        <v>0.0001634231593925506</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.00272298650816083</v>
+        <v>2.066748129436746e-05</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.004344434011727571</v>
+        <v>0.0001061266957549378</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01975430175662041</v>
+        <v>5.948857142357156e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1018017828464508</v>
+        <v>0.0002492911298759282</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0128833893686533</v>
+        <v>5.385172698879614e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.05302686616778374</v>
+        <v>9.010566282086074e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.02663053944706917</v>
+        <v>7.596390787512064e-06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.05129071325063705</v>
+        <v>0.0001514065079391003</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.01684296317398548</v>
+        <v>5.649985541822389e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0006298068910837173</v>
+        <v>3.679845394799486e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.04623309522867203</v>
+        <v>6.286385178100318e-05</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.004180599004030228</v>
+        <v>2.518339897505939e-06</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.03300882875919342</v>
+        <v>0.0001712415687507018</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0277280043810606</v>
+        <v>5.362235970096663e-05</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.02199049666523933</v>
+        <v>6.68250722810626e-05</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.003947626799345016</v>
+        <v>3.641784132923931e-06</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.04461454972624779</v>
+        <v>0.0001124971167882904</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01749347895383835</v>
+        <v>3.280120290583e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.01310320012271404</v>
+        <v>2.101906648022123e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.02309484034776688</v>
+        <v>4.904096203972585e-05</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.05126170441508293</v>
+        <v>2.490686347300652e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.005598020739853382</v>
+        <v>0.0001243765582330525</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.006117299664765596</v>
+        <v>0.0001451606367481872</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.01507003419101238</v>
+        <v>0.0001890704588731751</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01949442736804485</v>
+        <v>3.120230758213438e-05</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.003078053239732981</v>
+        <v>9.869636414805427e-05</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.05300744995474815</v>
+        <v>1.534580587758683e-05</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.05403919517993927</v>
+        <v>0.0001457267353544012</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.005935311317443848</v>
+        <v>5.162079833098687e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.002167431637644768</v>
+        <v>3.56194723281078e-05</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02796841599047184</v>
+        <v>0.0001706971816020086</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.02205833047628403</v>
+        <v>5.19216300745029e-05</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.03464195877313614</v>
+        <v>9.095513087231666e-05</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.005702638067305088</v>
+        <v>9.542392945149913e-06</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.04850707203149796</v>
+        <v>0.0001289973297389224</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.01737946271896362</v>
+        <v>8.475824870401993e-06</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02640135586261749</v>
+        <v>2.865522583306301e-05</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.008576655760407448</v>
+        <v>4.213574720779434e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.005576861556619406</v>
+        <v>4.155690839979798e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.009329527616500854</v>
+        <v>0.0001706390321487561</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.008913579396903515</v>
+        <v>3.108791133854538e-06</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1084200292825699</v>
+        <v>2.103563565469813e-05</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03606671094894409</v>
+        <v>0.0002405786653980613</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.002494313754141331</v>
+        <v>0.0001304246834479272</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.005248419940471649</v>
+        <v>7.863876817282289e-05</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.03802705556154251</v>
+        <v>3.175515303155407e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.01558523345738649</v>
+        <v>2.187007339671254e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.005589612759649754</v>
+        <v>3.75410781998653e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.007432531099766493</v>
+        <v>0.0001042774820234627</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01535838469862938</v>
+        <v>5.361764124245383e-05</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.002569898962974548</v>
+        <v>8.243765478255227e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01032143458724022</v>
+        <v>4.309947689762339e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.004753006622195244</v>
+        <v>4.314210673328489e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.02424870431423187</v>
+        <v>7.904272933956236e-05</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0107392119243741</v>
+        <v>0.000167968450114131</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.03175603970885277</v>
+        <v>6.320500688161701e-05</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.002269883640110493</v>
+        <v>3.931413448299281e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.02471088618040085</v>
+        <v>8.240250281232875e-06</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.02203634567558765</v>
+        <v>6.83101243339479e-05</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.002790269441902637</v>
+        <v>8.871954923961312e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0009887428022921085</v>
+        <v>0.0001355179265374318</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01825403608381748</v>
+        <v>2.874599158531055e-05</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.002931427676230669</v>
+        <v>6.502319592982531e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.01158789545297623</v>
+        <v>8.445711864624172e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0023620689753443</v>
+        <v>9.713500912766904e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.01429750118404627</v>
+        <v>8.257808985945303e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.03707843646407127</v>
+        <v>7.280324643943459e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.01671922020614147</v>
+        <v>1.393225829815492e-06</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.007259863428771496</v>
+        <v>1.371270627714694e-06</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002123698126524687</v>
+        <v>1.435308149666525e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.04727816581726074</v>
+        <v>3.115346044069156e-05</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.01379426103085279</v>
+        <v>1.928487108671106e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.006734445225447416</v>
+        <v>1.246563169843284e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.01293251849710941</v>
+        <v>2.480787770764437e-05</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.005293264053761959</v>
+        <v>2.611778108985163e-05</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.01254746876657009</v>
+        <v>6.192229920998216e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.01478577218949795</v>
+        <v>8.711525879334658e-05</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0212175901979208</v>
+        <v>7.656376692466438e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.009346412494778633</v>
+        <v>7.212260970845819e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.04084492847323418</v>
+        <v>9.845624299487099e-05</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.031680628657341</v>
+        <v>2.897000013035722e-05</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.07610173523426056</v>
+        <v>6.618309998884797e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.01037327572703362</v>
+        <v>6.306174327619374e-05</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.002322782995179296</v>
+        <v>2.325326386198867e-05</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02568789012730122</v>
+        <v>0.0001945614203577861</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.01824776083230972</v>
+        <v>4.161739707342349e-05</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.03007044643163681</v>
+        <v>0.0001102497626561671</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001091984333470464</v>
+        <v>4.156550130574033e-05</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0403733029961586</v>
+        <v>9.76937371888198e-05</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.02913432754576206</v>
+        <v>2.757054244284518e-05</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.01410173624753952</v>
+        <v>2.503965515643358e-05</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.02204821072518826</v>
+        <v>2.014311940001789e-05</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.01217825710773468</v>
+        <v>3.408066913834773e-05</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0006711384048685431</v>
+        <v>0.0002240671310573816</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.009708542376756668</v>
+        <v>0.0001017417016555555</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04318524897098541</v>
+        <v>0.0001756510027917102</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01101253926753998</v>
+        <v>0.0001276210095966235</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02679337002336979</v>
+        <v>0.0001539119111839682</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.008857926353812218</v>
+        <v>1.320474530075444e-05</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.02129599824547768</v>
+        <v>9.878941636998206e-05</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01910114102065563</v>
+        <v>8.907033770810813e-05</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.01442377828061581</v>
+        <v>3.210777140338905e-05</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.05279998481273651</v>
+        <v>6.393679359462112e-05</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.03885854780673981</v>
+        <v>9.310065797762945e-05</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02426140382885933</v>
+        <v>0.0001375442370772362</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01370736956596375</v>
+        <v>0.0001021385687636212</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.008922290056943893</v>
+        <v>6.593899161089212e-05</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.02142512053251266</v>
+        <v>5.370668441173621e-05</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.003675260348245502</v>
+        <v>4.600562897394411e-05</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01859917491674423</v>
+        <v>1.418718602508307e-05</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.04650051146745682</v>
+        <v>0.0001490455470047891</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01996774598956108</v>
+        <v>3.463673056103289e-05</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.03209981322288513</v>
+        <v>0.0002752907166723162</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01183719653636217</v>
+        <v>1.038084519677795e-05</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.02790356427431107</v>
+        <v>0.0002713850990403444</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.01698098331689835</v>
+        <v>0.0001446290261810645</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.1272857487201691</v>
+        <v>3.438871135585941e-05</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001055099070072174</v>
+        <v>3.097085209446959e-05</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.005722253583371639</v>
+        <v>3.402948277653195e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0001625073055038229</v>
+        <v>2.030251522455728e-10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003670740406960249</v>
+        <v>3.950492910576031e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.533721898449585e-05</v>
+        <v>3.046680063789609e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009331564069725573</v>
+        <v>9.303640524649381e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001097588567063212</v>
+        <v>7.124146828019207e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001307672588154674</v>
+        <v>1.943373639790025e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004255551612004638</v>
+        <v>7.302858762159303e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005912304040975869</v>
+        <v>2.739471050006159e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00065939238993451</v>
+        <v>2.764710593794462e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002234159910585731</v>
+        <v>1.713171826622784e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003435318591073155</v>
+        <v>4.346865267734756e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.02252727933228e-05</v>
+        <v>3.473166998446686e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0004990622983314097</v>
+        <v>1.130852567143847e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0002625968481879681</v>
+        <v>1.333903743017117e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001154388766735792</v>
+        <v>1.513963887589398e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002413186739431694</v>
+        <v>5.129834335093619e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001780540042091161</v>
+        <v>1.411878702839431e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000681525852996856</v>
+        <v>3.386895652823796e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>0.000188314777915366</v>
+        <v>1.559517492921714e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00041594059439376</v>
+        <v>2.698130252554165e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.658635457919445e-05</v>
+        <v>8.700066445044286e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0002292959106853232</v>
+        <v>1.439983776663212e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003594657173380256</v>
+        <v>5.157219540308233e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001808006782084703</v>
+        <v>5.194793484264437e-10</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.908408249728382e-05</v>
+        <v>1.976443897433455e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000536738836672157</v>
+        <v>1.009973527033026e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0002643791376613081</v>
+        <v>1.779901559473274e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002589089854154736</v>
+        <v>2.550426358993718e-08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0001823353377403691</v>
+        <v>5.74426284316587e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001477868936490268</v>
+        <v>2.033282697766481e-08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0001958820794243366</v>
+        <v>9.136059908598781e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.366581950103864e-05</v>
+        <v>3.386417368744787e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.626610411331058e-05</v>
+        <v>1.540501948227302e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.015810115262866e-05</v>
+        <v>8.951936969481267e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.627723733894527e-05</v>
+        <v>2.399347565074095e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.000165001314599067</v>
+        <v>2.7566601445983e-08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0005129930796101689</v>
+        <v>1.486855438770363e-08</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0004245954041834921</v>
+        <v>2.090404116472655e-08</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001317017304245383</v>
+        <v>2.408064858627768e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.00026314752176404</v>
+        <v>2.128249354527156e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.000236154068261385</v>
+        <v>8.489512204334915e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0003279149241279811</v>
+        <v>9.373423814906801e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0002231803664471954</v>
+        <v>4.882160453689721e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.97034551599063e-05</v>
+        <v>3.765283640433381e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0002602206950541586</v>
+        <v>4.844596279696134e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0002756398171186447</v>
+        <v>1.851344855197112e-08</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002395435236394405</v>
+        <v>2.205485749584568e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0004316969425417483</v>
+        <v>1.149877881800876e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.445483788615093e-05</v>
+        <v>1.947604744145792e-09</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.692317351233214e-05</v>
+        <v>2.436651769244236e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0003603432851377875</v>
+        <v>1.266818983047813e-09</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0006580305634997785</v>
+        <v>3.67835584214049e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.000418921816162765</v>
+        <v>3.467373721477429e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0002177967253373936</v>
+        <v>1.269310523355216e-08</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001899121562018991</v>
+        <v>4.434961908827972e-08</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005346187390387058</v>
+        <v>6.028759713672116e-08</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0005369714926928282</v>
+        <v>1.375388780644471e-08</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.533456614008173e-05</v>
+        <v>1.116099213049893e-08</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0009622533107176423</v>
+        <v>4.531333885893218e-08</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.000657912518363446</v>
+        <v>1.481341493914101e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001465335371904075</v>
+        <v>1.115594727707503e-08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003492776013445109</v>
+        <v>3.351025412712261e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0005166225600987673</v>
+        <v>7.22811819287017e-08</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001288246130570769</v>
+        <v>6.377255612477484e-09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0004360439488664269</v>
+        <v>1.140568173241263e-08</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.339325333712623e-05</v>
+        <v>1.172163610618782e-08</v>
       </c>
       <c r="BO9" t="n">
-        <v>9.29082598304376e-05</v>
+        <v>5.946507730669737e-10</v>
       </c>
       <c r="BP9" t="n">
-        <v>8.740630437387154e-05</v>
+        <v>4.941675513236987e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0001695942773949355</v>
+        <v>8.480824043033408e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0002502007118891925</v>
+        <v>1.050726083917652e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>5.276987212710083e-05</v>
+        <v>1.416623707228837e-08</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0001371926628053188</v>
+        <v>1.077951772288088e-08</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.089000529143959e-05</v>
+        <v>2.501766438456343e-08</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001302944030612707</v>
+        <v>2.152306421976391e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001800228492356837</v>
+        <v>5.000477365513234e-09</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0002044078282779083</v>
+        <v>2.597047465968672e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0001010378473438323</v>
+        <v>3.395038694620212e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0001814131246646866</v>
+        <v>3.571891893372481e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001317189598921686</v>
+        <v>2.879022797941388e-09</v>
       </c>
       <c r="CB9" t="n">
-        <v>7.511259173043072e-05</v>
+        <v>1.852229036813924e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.095192995620891e-05</v>
+        <v>5.765140365099342e-09</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001724522007862106</v>
+        <v>3.087699873560723e-09</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.000619681435637176</v>
+        <v>1.258426918226974e-09</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0001032346626743674</v>
+        <v>4.240699347235477e-09</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0001043530501192436</v>
+        <v>3.609515797364793e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001148991723312065</v>
+        <v>3.280193894283912e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001485629036324099</v>
+        <v>7.616643316055161e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002266421215608716</v>
+        <v>4.063967828926707e-09</v>
       </c>
       <c r="CK9" t="n">
-        <v>7.059287599986419e-05</v>
+        <v>3.055255159978287e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0001690173521637917</v>
+        <v>2.242160235255142e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0008805063553154469</v>
+        <v>1.143378014489826e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0001358927838737145</v>
+        <v>1.02522728084864e-08</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0001872565189842135</v>
+        <v>2.497306894611029e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001095279818400741</v>
+        <v>2.493849571294504e-08</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0005429125158116221</v>
+        <v>3.552477068069493e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0007014228613115847</v>
+        <v>9.302812742362221e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0006165137747302651</v>
+        <v>2.561841405679388e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0003684494295157492</v>
+        <v>7.609652463713701e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0003251582093071193</v>
+        <v>2.42979183440184e-08</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0001656257372815162</v>
+        <v>2.057261028198809e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0005676117725670338</v>
+        <v>6.115013828633664e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>9.615143062546849e-05</v>
+        <v>3.389895031347123e-09</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0002930252230726182</v>
+        <v>3.420055127989485e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001352988183498383</v>
+        <v>3.661965397583344e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>7.947250560391694e-05</v>
+        <v>5.698228999762023e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0002206504868809134</v>
+        <v>1.975438479462355e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0001799060119083151</v>
+        <v>3.230793410580191e-10</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001723882887745276</v>
+        <v>4.096753603022307e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0002806545817293227</v>
+        <v>8.900656212063041e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.000551530160009861</v>
+        <v>3.965097050695476e-08</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0001470568822696805</v>
+        <v>4.137658038416703e-08</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0005524563021026552</v>
+        <v>8.282388108682426e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001231647795066237</v>
+        <v>1.33569599825023e-08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001186374807730317</v>
+        <v>1.384858716590998e-08</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001345831406069919</v>
+        <v>1.610623812098311e-08</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002396773343207315</v>
+        <v>3.274387649909727e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0008612981182523072</v>
+        <v>5.06603337058209e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0002336816105525941</v>
+        <v>3.077517618521597e-08</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001059314017766155</v>
+        <v>3.074674026493085e-08</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0002681733458302915</v>
+        <v>1.286779038878194e-08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004239326517563313</v>
+        <v>8.330169443127033e-09</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001678353291936219</v>
+        <v>1.506101199311161e-08</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0004054759338032454</v>
+        <v>2.119612485529387e-09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0003566736704669893</v>
+        <v>1.046543829374968e-08</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.000307325943140313</v>
+        <v>1.172905150781389e-08</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0002277263847645372</v>
+        <v>4.123501096131577e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>8.48897616378963e-05</v>
+        <v>1.205712951701798e-08</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0004221591807436198</v>
+        <v>2.625244022169682e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0001742387830745429</v>
+        <v>2.853150604664734e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004962297971360385</v>
+        <v>5.481942899621117e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0003069161321036518</v>
+        <v>4.493176319897429e-08</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0001505095133325085</v>
+        <v>1.590006348806128e-08</v>
       </c>
       <c r="EC9" t="n">
-        <v>7.643689605174586e-05</v>
+        <v>2.518347841373725e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0003267455904278904</v>
+        <v>2.636901363928246e-09</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0007616282673552632</v>
+        <v>1.092618795439648e-08</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0005612136446870863</v>
+        <v>4.12322309628621e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0008951883064582944</v>
+        <v>9.146780222124562e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>6.432541704270989e-05</v>
+        <v>2.198322857083213e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001813791604945436</v>
+        <v>7.482812591774746e-09</v>
       </c>
       <c r="EJ9" t="n">
-        <v>9.435112588107586e-05</v>
+        <v>8.518672878210509e-09</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0003271212626714259</v>
+        <v>1.214474920629982e-08</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0003212945302948356</v>
+        <v>5.059634489157361e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0001746903581079096</v>
+        <v>4.89309437412544e-09</v>
       </c>
       <c r="EN9" t="n">
-        <v>5.940150003880262e-05</v>
+        <v>1.3412427612991e-08</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0002581137814559042</v>
+        <v>1.592377607551043e-08</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0003381170681677759</v>
+        <v>1.111801317676964e-08</v>
       </c>
       <c r="EQ9" t="n">
-        <v>8.285448711831123e-05</v>
+        <v>8.394271944212051e-09</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.000418306648498401</v>
+        <v>8.386033201190912e-09</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002797093475237489</v>
+        <v>5.662646351822787e-09</v>
       </c>
       <c r="ET9" t="n">
-        <v>4.762167372973636e-05</v>
+        <v>2.762393425115306e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0005885777645744383</v>
+        <v>5.459663388052149e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004540204245131463</v>
+        <v>1.30800845710155e-08</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0001851621636888012</v>
+        <v>7.279845615215663e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.000229274810408242</v>
+        <v>2.30703056658399e-09</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0005826235865242779</v>
+        <v>7.940622381852336e-09</v>
       </c>
       <c r="EZ9" t="n">
-        <v>3.88164771720767e-05</v>
+        <v>1.866501175840085e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>1.325404082308523e-05</v>
+        <v>1.433976493103728e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.000108859094325453</v>
+        <v>4.976866696537741e-10</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001204452273668721</v>
+        <v>8.476191304396252e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0003317566006444395</v>
+        <v>7.64401075770138e-09</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001440963242202997</v>
+        <v>5.808615810565243e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0002812842139974236</v>
+        <v>6.000974384079427e-09</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001144496854976751</v>
+        <v>1.735445565032023e-09</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0002643500629346818</v>
+        <v>7.75365904814862e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0003253495669923723</v>
+        <v>2.763906081781897e-08</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0005794989410787821</v>
+        <v>1.122195847358398e-08</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0002302719076396897</v>
+        <v>2.870169879543027e-08</v>
       </c>
       <c r="FL9" t="n">
-        <v>6.936895078979433e-05</v>
+        <v>1.016916773011189e-08</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001722056185826659</v>
+        <v>1.373377078728311e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0001363222399959341</v>
+        <v>2.676056531925042e-08</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002502445131540298</v>
+        <v>1.69878866529416e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0006497618742287159</v>
+        <v>3.459157582597072e-08</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0002649548696354032</v>
+        <v>3.135189530212301e-08</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0003005223697982728</v>
+        <v>3.094334388720199e-08</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.000502966227941215</v>
+        <v>6.289870668751973e-08</v>
       </c>
       <c r="FT9" t="n">
-        <v>9.294912160839885e-05</v>
+        <v>6.899752769129464e-09</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0002811792655847967</v>
+        <v>1.902777047035897e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0001041432988131419</v>
+        <v>7.005019675432322e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>2.798574132611975e-05</v>
+        <v>3.680978366560339e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002305346424691379</v>
+        <v>6.239942340613425e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.000729277147911489</v>
+        <v>1.159303675279943e-08</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001017888644128107</v>
+        <v>2.085360506498546e-08</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0001959515066118911</v>
+        <v>1.850755637633483e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.62962078320561e-05</v>
+        <v>2.005306143360031e-08</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.000156287889694795</v>
+        <v>1.329558241280893e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0003006122133228928</v>
+        <v>1.648277425658762e-08</v>
       </c>
       <c r="GE9" t="n">
-        <v>8.680026076035574e-05</v>
+        <v>1.542491290251746e-08</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0002097943070111796</v>
+        <v>4.034950151776684e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0002751450520008802</v>
+        <v>3.066126463835417e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.180318832397461</v>
+        <v>0.5848846435546875</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2624476253986359</v>
+        <v>0.07003936171531677</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03602723777294159</v>
+        <v>1.371728539466858</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2170795798301697</v>
+        <v>0.5881034731864929</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1146289333701134</v>
+        <v>0.619350790977478</v>
       </c>
       <c r="F10" t="n">
-        <v>0.824756920337677</v>
+        <v>1.483222246170044</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2843971848487854</v>
+        <v>0.2449263781309128</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2468066364526749</v>
+        <v>0.7028997540473938</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1478591710329056</v>
+        <v>0.651999831199646</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8320124745368958</v>
+        <v>0.5539077520370483</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2442663460969925</v>
+        <v>0.2859893143177032</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08131936937570572</v>
+        <v>1.813968658447266</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1893030107021332</v>
+        <v>0.2350879311561584</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1216944605112076</v>
+        <v>1.163515090942383</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7159577012062073</v>
+        <v>2.460204839706421</v>
       </c>
       <c r="P10" t="n">
-        <v>0.517544150352478</v>
+        <v>0.2104295790195465</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.345853716135025</v>
+        <v>0.5330830216407776</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05499375611543655</v>
+        <v>1.027936577796936</v>
       </c>
       <c r="S10" t="n">
-        <v>0.122728168964386</v>
+        <v>0.1049882024526596</v>
       </c>
       <c r="T10" t="n">
-        <v>0.301302045583725</v>
+        <v>0.4458854794502258</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08859209716320038</v>
+        <v>0.5477308034896851</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1868656277656555</v>
+        <v>0.002783045172691345</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4058549702167511</v>
+        <v>0.204473152756691</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1560489535331726</v>
+        <v>0.1213886588811874</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.210093691945076</v>
+        <v>0.4285227060317993</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1270359307527542</v>
+        <v>0.1756923645734787</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01843433082103729</v>
+        <v>0.1334753036499023</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2663926184177399</v>
+        <v>0.2844670414924622</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1188983246684074</v>
+        <v>0.06491955369710922</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.149054080247879</v>
+        <v>0.4080002307891846</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0740465372800827</v>
+        <v>0.1097308173775673</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1120143160223961</v>
+        <v>0.125984251499176</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1418112367391586</v>
+        <v>0.5366302132606506</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.05035024881362915</v>
+        <v>0.2583291232585907</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05687310546636581</v>
+        <v>0.1343338936567307</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.03541107103228569</v>
+        <v>0.6521579027175903</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.2485543936491013</v>
+        <v>0.1930579245090485</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1174021139740944</v>
+        <v>0.05275344848632812</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1018578112125397</v>
+        <v>0.2655395567417145</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.18299899995327</v>
+        <v>0.4317006468772888</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03424657136201859</v>
+        <v>0.7594559788703918</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.05385412648320198</v>
+        <v>0.07194268703460693</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.03006621822714806</v>
+        <v>0.1531426310539246</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.141258493065834</v>
+        <v>0.1867043524980545</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01079247612506151</v>
+        <v>0.03339933976531029</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.7277436852455139</v>
+        <v>0.08120882511138916</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2824447453022003</v>
+        <v>0.8813360929489136</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1099474802613258</v>
+        <v>0.7129140496253967</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1571962535381317</v>
+        <v>0.1728441119194031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5958960652351379</v>
+        <v>0.4892546236515045</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.6714555621147156</v>
+        <v>1.582449555397034</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.05543580651283264</v>
+        <v>0.468798041343689</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.353589653968811</v>
+        <v>0.3306079208850861</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1189827397465706</v>
+        <v>0.1486810296773911</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.2096754014492035</v>
+        <v>0.307512104511261</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.4472244381904602</v>
+        <v>0.4695419073104858</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1104241758584976</v>
+        <v>0.2256154716014862</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.165772870182991</v>
+        <v>0.09923109412193298</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.05268099904060364</v>
+        <v>1.17997670173645</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.03570632264018059</v>
+        <v>0.768659770488739</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.3716038465499878</v>
+        <v>0.0421411320567131</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.1683153361082077</v>
+        <v>0.1908360570669174</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.04659848660230637</v>
+        <v>0.2998316884040833</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.02140155807137489</v>
+        <v>0.5671635866165161</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2061213105916977</v>
+        <v>0.2433558851480484</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.05190711468458176</v>
+        <v>0.8958279490470886</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2324418872594833</v>
+        <v>0.006030023097991943</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1896874457597733</v>
+        <v>0.06480519473552704</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1815392524003983</v>
+        <v>0.1017649248242378</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.1858390867710114</v>
+        <v>0.1734987199306488</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.1701963841915131</v>
+        <v>0.1747335642576218</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.1692915707826614</v>
+        <v>0.2440392822027206</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.3561715483665466</v>
+        <v>0.07315399497747421</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2577700614929199</v>
+        <v>0.1201103627681732</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.105206161737442</v>
+        <v>0.6262916922569275</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1410582214593887</v>
+        <v>0.6708921194076538</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.387031614780426</v>
+        <v>0.1901224702596664</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.4585424661636353</v>
+        <v>0.7034153342247009</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.05101502686738968</v>
+        <v>0.3462085425853729</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.2427727282047272</v>
+        <v>0.1112069487571716</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0170366894453764</v>
+        <v>0.07022160291671753</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.2071567475795746</v>
+        <v>0.07287240028381348</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2340685129165649</v>
+        <v>0.05601990222930908</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.009120514616370201</v>
+        <v>0.5408768057823181</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0006161481142044067</v>
+        <v>0.1264802813529968</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.08329862356185913</v>
+        <v>0.1124960035085678</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.1400411128997803</v>
+        <v>0.1481123417615891</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.02694472298026085</v>
+        <v>0.1375765800476074</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2237138301134109</v>
+        <v>0.08195298910140991</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0202200785279274</v>
+        <v>0.08892946690320969</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.03247847408056259</v>
+        <v>0.1525468230247498</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.06939671188592911</v>
+        <v>0.09991998225450516</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.004537966102361679</v>
+        <v>0.2370522916316986</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.006920285522937775</v>
+        <v>0.1604753881692886</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.625977098941803</v>
+        <v>0.292252391576767</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1016014590859413</v>
+        <v>0.5923437476158142</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.08734869211912155</v>
+        <v>0.461259514093399</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.04722239077091217</v>
+        <v>0.1652331799268723</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.02921108342707157</v>
+        <v>0.03871528059244156</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.1915698796510696</v>
+        <v>0.1025032475590706</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.2226179391145706</v>
+        <v>0.1166781410574913</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.01289805956184864</v>
+        <v>0.5053735375404358</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02510286867618561</v>
+        <v>0.1047535911202431</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.07357688993215561</v>
+        <v>0.3172684907913208</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.1475271880626678</v>
+        <v>0.3495361804962158</v>
       </c>
       <c r="DB10" t="n">
-        <v>6.191432476043701e-06</v>
+        <v>0.144146203994751</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.2236250042915344</v>
+        <v>0.0201024953275919</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.03981001675128937</v>
+        <v>0.0994885042309761</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08251099288463593</v>
+        <v>0.1424831300973892</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.109473742544651</v>
+        <v>0.1321528553962708</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.04461254179477692</v>
+        <v>0.6422188878059387</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1613059341907501</v>
+        <v>0.2733647227287292</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.3635796308517456</v>
+        <v>0.1941564381122589</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002030434086918831</v>
+        <v>0.262524276971817</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.07045847177505493</v>
+        <v>0.432799905538559</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2261217683553696</v>
+        <v>0.2326010167598724</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.1083736270666122</v>
+        <v>0.5219295620918274</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.1072840914130211</v>
+        <v>0.02204790152609348</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.008241094648838043</v>
+        <v>0.1793106496334076</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.1055444628000259</v>
+        <v>0.6419658064842224</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0298868790268898</v>
+        <v>0.07922375947237015</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.04442330077290535</v>
+        <v>0.3435224592685699</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1124017238616943</v>
+        <v>0.4133778810501099</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1855147331953049</v>
+        <v>0.2228248417377472</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.4045686423778534</v>
+        <v>0.2385864108800888</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.04623319208621979</v>
+        <v>0.4878709316253662</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01469737198203802</v>
+        <v>0.1388528794050217</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1713905185461044</v>
+        <v>0.515184223651886</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.02710531279444695</v>
+        <v>0.6427204608917236</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.03964009135961533</v>
+        <v>0.7106972336769104</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02378075942397118</v>
+        <v>0.2253076732158661</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.3302265703678131</v>
+        <v>0.5810720920562744</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.02017518505454063</v>
+        <v>0.1263360679149628</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02929426357150078</v>
+        <v>0.2373557835817337</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.125989094376564</v>
+        <v>0.1232561841607094</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.1558857858181</v>
+        <v>0.1578329056501389</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.165084645152092</v>
+        <v>0.1415406912565231</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02859915792942047</v>
+        <v>0.4527249932289124</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07607606053352356</v>
+        <v>0.004408175125718117</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01644260250031948</v>
+        <v>0.4152713418006897</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.02583561837673187</v>
+        <v>0.1092369481921196</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.009257040917873383</v>
+        <v>0.01152574829757214</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03606799617409706</v>
+        <v>0.02155927568674088</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.04177474975585938</v>
+        <v>0.1175269111990929</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.07893306761980057</v>
+        <v>0.008628770709037781</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.2749474346637726</v>
+        <v>0.1995585560798645</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.06947876513004303</v>
+        <v>0.1935864388942719</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1030310243368149</v>
+        <v>0.03053360432386398</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.3104412257671356</v>
+        <v>0.1627426445484161</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1382138133049011</v>
+        <v>0.2902105152606964</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.1710902601480484</v>
+        <v>0.1830323338508606</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1514442712068558</v>
+        <v>0.1612802296876907</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.1365577876567841</v>
+        <v>0.2081024944782257</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.154307559132576</v>
+        <v>0.03870616853237152</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1827547401189804</v>
+        <v>0.01948732882738113</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.006807371973991394</v>
+        <v>0.3967071175575256</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.04828403517603874</v>
+        <v>0.144148975610733</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.07718504220247269</v>
+        <v>0.1222541630268097</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.1069734692573547</v>
+        <v>0.3370934426784515</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.05345487222075462</v>
+        <v>0.1998439729213715</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2686589062213898</v>
+        <v>0.08246991038322449</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.03132621571421623</v>
+        <v>0.06257987767457962</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.1046399474143982</v>
+        <v>0.2375799864530563</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07016362249851227</v>
+        <v>0.3680876195430756</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0588342659175396</v>
+        <v>0.6143237352371216</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01723785698413849</v>
+        <v>0.2994651794433594</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.09701593965291977</v>
+        <v>0.04778685420751572</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01401578821241856</v>
+        <v>0.4175926744937897</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.06058432534337044</v>
+        <v>0.2781196236610413</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01227173767983913</v>
+        <v>0.4359074234962463</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.02701780572533607</v>
+        <v>0.4850861430168152</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.2454353868961334</v>
+        <v>0.2713158130645752</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.1534387916326523</v>
+        <v>0.3373424410820007</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.1370709389448166</v>
+        <v>0.7695785760879517</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.09993056952953339</v>
+        <v>0.1202555298805237</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.234009325504303</v>
+        <v>0.6619278192520142</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.3053976893424988</v>
+        <v>0.4138425290584564</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.1054039597511292</v>
+        <v>0.1008172035217285</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.02449970506131649</v>
+        <v>0.3672768473625183</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.005827286280691624</v>
+        <v>0.9430080056190491</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1003322303295135</v>
+        <v>0.3014031946659088</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02141768299043179</v>
+        <v>0.7141110897064209</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.06822192668914795</v>
+        <v>0.4742826819419861</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.05670862272381783</v>
+        <v>0.02296196669340134</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1061685085296631</v>
+        <v>0.09068579971790314</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.07953757047653198</v>
+        <v>0.1115282252430916</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.07594138383865356</v>
+        <v>0.3244221210479736</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.130971685051918</v>
+        <v>0.5502086281776428</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.04311869293451309</v>
+        <v>0.2385734170675278</v>
       </c>
     </row>
   </sheetData>
